--- a/template/イベント情報入力シート.xlsx
+++ b/template/イベント情報入力シート.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="基本情報" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="タイムテーブル" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="資料リンク" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="関連書籍" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="概要・お知らせ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本情報" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タイムテーブル" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料リンク" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連書籍" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要・お知らせ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>色（blue/green/orange/purple）</t>
+          <t>色（blue/blueDeep/green/greenDeep/orange/purple）</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>blueDeep</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr"/>
@@ -877,7 +877,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr"/>
@@ -903,7 +903,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr"/>

--- a/template/イベント情報入力シート.xlsx
+++ b/template/イベント情報入力シート.xlsx
@@ -175,7 +175,7 @@
     <author>ひな形</author>
   </authors>
   <commentList>
-    <comment ref="A17" authorId="0" shapeId="0">
+    <comment ref="A18" authorId="0" shapeId="0">
       <text>
         <t>例: 1日目 / 2日目</t>
       </text>
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -760,124 +760,128 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>LINE追加ポップアップ</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>JSON: linePromo。LINE友だち追加を促すポップアップを出すか。true=表示／false・空欄=非表示（既定）。チラシQR等で既にLINEから誘導しているイベントは false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>会場マップ補足</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>会場は筑波大学附属小学校です。詳しい会場割りは当日の掲示・配布物をご確認ください。</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>JSON: venue.mapNote（任意）</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>■ 開催日ごとの設定（dates[]）</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>ラベル</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>日付 / 曜日</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>1日目</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-04 / 火</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>10:00〜16:15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>1日目</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04 / 火</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>10:00〜16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t>2日目</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>2026-08-05 / 水</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>8:50〜16:00</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>■ 会場一覧（rooms[]）※並行セッションがある場合</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>会場名</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>色（blue/blueDeep/green/greenDeep/orange/purple）</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>（空欄可）</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>A会場</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>blueDeep</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>B会場</t>
+          <t>A会場</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>blueDeep</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr"/>
@@ -885,12 +889,12 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>C会場</t>
+          <t>B会場</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr"/>
@@ -898,21 +902,34 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
+          <t>C会場</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
           <t>D会場</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr"/>
+      <c r="C27" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A22:C22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/template/イベント情報入力シート.xlsx
+++ b/template/イベント情報入力シート.xlsx
@@ -175,7 +175,7 @@
     <author>ひな形</author>
   </authors>
   <commentList>
-    <comment ref="A18" authorId="0" shapeId="0">
+    <comment ref="A23" authorId="0" shapeId="0">
       <text>
         <t>例: 1日目 / 2日目</t>
       </text>
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -617,318 +617,387 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>JSON: logoMain。ホーム画面追加時のアプリ名</t>
+          <t>JSON: logoMain。ヘッダー1行目。空欄なら研究会名</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>アイコン3文字</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>全算研</t>
-        </is>
-      </c>
+          <t>PWA表示名</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>アプリアイコンに出る先頭3文字（logoMain 先頭3文字）</t>
+          <t>JSON: appName（任意）。ホーム画面のアプリ名を更に短くしたいときだけ記入（例: 算サマ2026）。空欄ならアプリ名（logoMain）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ロゴ補足</t>
+          <t>アイコン3文字</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>全国算数授業研究大会2026</t>
+          <t>全算研</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>JSON: logoSub（任意）</t>
+          <t>JSON: iconLabel（任意）。アプリアイコンに出る文字。空欄ならアプリ名の先頭3文字</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>テーマ</t>
+          <t>ロゴ補足</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>探究がはじまる！算数で育てたい子どもの「見る目」</t>
+          <t>全国算数授業研究大会2026</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>JSON: theme</t>
+          <t>JSON: logoSub（任意）。ヘッダー2行目は研究会名を優先し、これは予備</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>会場名</t>
+          <t>テーマ</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>筑波大学附属小学校</t>
+          <t>探究がはじまる！算数で育てたい子どもの「見る目」</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>JSON: venueName</t>
+          <t>JSON: theme。「――」等で区切るとサブテーマが自動で改行される</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>開催日（表示用）</t>
+          <t>会場名</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>令和8年8月4日(火)・5日(水)</t>
+          <t>筑波大学附属小学校</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>JSON: dateRange。チラシ表記そのまま</t>
+          <t>JSON: venueName</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ブランド色</t>
+          <t>開催日（表示用）</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>#f59e0b</t>
+          <t>令和8年8月4日(火)・5日(水)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>JSON: brandColor。メイン1色の16進カラー</t>
+          <t>JSON: dateRange。チラシ表記そのまま</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>イベントID</t>
+          <t>主催</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-zensanken-37</t>
+          <t>全国算数授業研究会</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ファイル名 events/&lt;id&gt;.json。半角英数・ハイフン・アンダースコアのみ</t>
+          <t>JSON: organizer（任意）。概要・お知らせの1つ目のカードに表示。複数は「／」区切り</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>並び順日付</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+          <t>共催</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>events.json の sortDate。YYYY-MM-DD</t>
+          <t>JSON: coOrganizer（任意）。ある場合のみ記入。無ければ空欄で行が出ない</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>LINE追加ポップアップ</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>協力</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>JSON: linePromo。LINE友だち追加を促すポップアップを出すか。true=表示／false・空欄=非表示（既定）。チラシQR等で既にLINEから誘導しているイベントは false</t>
+          <t>JSON: cooperation（任意）。ある場合のみ記入</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>後援</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>JSON: support（任意）。ある場合のみ記入。複数は「／」区切り</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>ブランド色</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>#f59e0b</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>JSON: brandColor。メイン1色の16進カラー</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>イベントID</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2026-zensanken-37</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>ファイル名 events/&lt;id&gt;.json。半角英数・ハイフン・アンダースコアのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>並び順日付</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>events.json の sortDate。YYYY-MM-DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>LINE追加ポップアップ</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>JSON: linePromo。LINE友だち追加を促すポップアップを出すか。true=表示／false・空欄=非表示（既定）。チラシQR等で既にLINEから誘導しているイベントは false</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>会場マップ補足</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>会場は筑波大学附属小学校です。詳しい会場割りは当日の掲示・配布物をご確認ください。</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>JSON: venue.mapNote（任意）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>■ 開催日ごとの設定（dates[]）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>ラベル</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>日付 / 曜日</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>1日目</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-04 / 火</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>10:00〜16:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>2日目</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-05 / 水</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>8:50〜16:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>■ 会場一覧（rooms[]）※並行セッションがある場合</t>
+          <t>■ 開催日ごとの設定（dates[]）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>会場名</t>
+          <t>ラベル</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>色（blue/blueDeep/green/greenDeep/orange/purple）</t>
+          <t>日付 / 曜日</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>（空欄可）</t>
+          <t>時間</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>A会場</t>
+          <t>1日目</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>blueDeep</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr"/>
+          <t>2026-08-04 / 火</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>10:00〜16:15</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
+          <t>2日目</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05 / 水</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>8:50〜16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>■ 会場一覧（rooms[]）※並行セッションがある場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>会場名</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>色（blue/blueDeep/green/greenDeep/orange/purple）</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>（空欄可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>A会場</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>blueDeep</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
           <t>B会場</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>C会場</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>D会場</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr"/>
+      <c r="C32" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A22:C22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/template/イベント情報入力シート.xlsx
+++ b/template/イベント情報入力シート.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="1" r:id="R9ceb0e7de2144db4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="R6ac4f339fb41446c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本情報" sheetId="3" r:id="R60679c3962374aa8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="開催日" sheetId="4" r:id="R0a8307bcccc24b4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会場" sheetId="5" r:id="Rf57b8fef841b47cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セッション" sheetId="6" r:id="Ra4ec484dc6c94081"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プログラム項目" sheetId="7" r:id="R1d15efa7fd73436a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料リンク" sheetId="8" r:id="R37e618b7ee124fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連書籍" sheetId="9" r:id="R8f811d77ef3c481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要・お知らせ" sheetId="10" r:id="Rb3a0b76ec4324236"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認" sheetId="11" r:id="R9d6bb351e45b40e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="1" r:id="R92c5771f67454bc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="R9faefbeae547480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本情報" sheetId="3" r:id="R10eff51424ad4728"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="開催日" sheetId="4" r:id="R85b60e9f19194fb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会場" sheetId="5" r:id="R94cee4d2af06427e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セッション" sheetId="6" r:id="Rb8cbbde3840d489f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プログラム項目" sheetId="7" r:id="R37bcc90d2fe945ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料リンク" sheetId="8" r:id="R79e14f46d83e48d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連書籍" sheetId="9" r:id="R106b5fc90efa4a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要・お知らせ" sheetId="10" r:id="Rd9a4dc4138964789"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認" sheetId="11" r:id="R9550b5f8208c481e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,8 +20,28 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={AD396C75-56C2-2C29-8063-4788677A97DC}</x:author>
-    <x:author>tc={43422C16-46C6-6A65-8974-378963A9C7E8}</x:author>
+    <x:author>tc={62B1246F-9BC5-9A18-3138-CA6A9085C3EC}</x:author>
+  </x:authors>
+  <x:commentList>
+    <x:comment ref="A3" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    資料が矛盾したときの採用順。判断できない場合は無理に順位を付けず、要確認シートへ記録します。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+  </x:commentList>
+</x:comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:authors>
+    <x:author>tc={07A0ECB9-8709-5CA9-0C34-EEE68AAA5605}</x:author>
+    <x:author>tc={EDA7FFB6-407E-6369-5245-DB0BA77D598D}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="A3" authorId="0">
@@ -48,11 +68,11 @@
 </x:comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={DC6C8553-7709-FA5F-7411-F475D298B126}</x:author>
-    <x:author>tc={86E109DB-1072-D3E8-2188-274C1C985D64}</x:author>
+    <x:author>tc={4032D6A1-2FD9-29E0-FF43-3A44EC59411B}</x:author>
+    <x:author>tc={EC798C26-A0B2-4406-AE60-A1507E8830B2}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="A3" authorId="0">
@@ -79,11 +99,12 @@
 </x:comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={AF175649-F41C-65B5-2EB6-0AF2FFA7161F}</x:author>
-    <x:author>tc={468BB692-D34D-1455-D890-17146C1FF036}</x:author>
+    <x:author>tc={8294C550-DF34-22FA-7AF3-1BA6051DD935}</x:author>
+    <x:author>tc={B2E96024-59FC-4AE2-2922-B81DDE300CCC}</x:author>
+    <x:author>tc={8F2C0F5C-C3F5-B497-05D4-CB05FF018764}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="A3" authorId="0">
@@ -106,16 +127,26 @@
         </x:r>
       </x:text>
     </x:comment>
+    <x:comment ref="G3" authorId="2">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    afterNote。セッションのカード直後に表示する補足です（例: 終了後に懇親会を予定）。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
   </x:commentList>
 </x:comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={5F8066C5-957B-0CA7-B46B-5499ABC81DDC}</x:author>
-    <x:author>tc={BD0FA2B3-28BC-B2E2-FFD2-8BE5600EA6DA}</x:author>
-    <x:author>tc={900A0A90-6C84-581E-DA86-45B310B77807}</x:author>
+    <x:author>tc={30A4B7D6-7F71-8869-053C-3625657D792A}</x:author>
+    <x:author>tc={F225F0DF-A967-EE81-1A2F-216A4A045EE1}</x:author>
+    <x:author>tc={B218E4C8-2BF2-E501-1BD0-F950C4CCF1F2}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="A3" authorId="0">
@@ -344,7 +375,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="なつき" id="{A60E5E94-04BA-4CF6-837C-AB1B77B12843}"/>
+  <xltc:person displayName="なつき" id="{95263565-8673-4D96-B8C3-79834C7CE147}"/>
 </xltc:personList>
 </file>
 
@@ -541,46 +572,57 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="A3" dT="2026-07-17T01:39:44.662" personId="{A60E5E94-04BA-4CF6-837C-AB1B77B12843}" id="{AD396C75-56C2-2C29-8063-4788677A97DC}">
-    <xltc:text>day1, day2…を使用。タイムテーブルの日付IDと一致させます。</xltc:text>
-  </xltc:threadedComment>
-  <xltc:threadedComment ref="E3" dT="2026-07-17T01:39:44.667" personId="{A60E5E94-04BA-4CF6-837C-AB1B77B12843}" id="{43422C16-46C6-6A65-8974-378963A9C7E8}">
-    <xltc:text>例: 受付8:30／9:00〜17:00。資料の表示を保ちます。</xltc:text>
+  <xltc:threadedComment ref="A3" dT="2026-07-17T01:51:00.906" personId="{95263565-8673-4D96-B8C3-79834C7CE147}" id="{62B1246F-9BC5-9A18-3138-CA6A9085C3EC}">
+    <xltc:text>資料が矛盾したときの採用順。判断できない場合は無理に順位を付けず、要確認シートへ記録します。</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
 </file>
 
 <file path=xl/threadedcomments/threadedcomment2.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="A3" dT="2026-07-17T01:39:44.673" personId="{A60E5E94-04BA-4CF6-837C-AB1B77B12843}" id="{DC6C8553-7709-FA5F-7411-F475D298B126}">
-    <xltc:text>JSONのid。タイムテーブルの会場IDと完全一致させます。表示名と同じでも構いません。</xltc:text>
+  <xltc:threadedComment ref="A3" dT="2026-07-17T01:51:00.927" personId="{95263565-8673-4D96-B8C3-79834C7CE147}" id="{07A0ECB9-8709-5CA9-0C34-EEE68AAA5605}">
+    <xltc:text>day1, day2…を使用。タイムテーブルの日付IDと一致させます。</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B3" dT="2026-07-17T01:39:44.673" personId="{A60E5E94-04BA-4CF6-837C-AB1B77B12843}" id="{86E109DB-1072-D3E8-2188-274C1C985D64}">
-    <xltc:text>JSONのname。例: 会場ID『講堂』、表示名『3階・講堂』。</xltc:text>
+  <xltc:threadedComment ref="E3" dT="2026-07-17T01:51:00.927" personId="{95263565-8673-4D96-B8C3-79834C7CE147}" id="{EDA7FFB6-407E-6369-5245-DB0BA77D598D}">
+    <xltc:text>例: 受付8:30／9:00〜17:00。資料の表示を保ちます。</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
 </file>
 
 <file path=xl/threadedcomments/threadedcomment3.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="A3" dT="2026-07-17T01:39:44.699" personId="{A60E5E94-04BA-4CF6-837C-AB1B77B12843}" id="{AF175649-F41C-65B5-2EB6-0AF2FFA7161F}">
-    <xltc:text>同じセッションにまとめる行は同じキー（例: day1-07）。時刻や区分が同じでも別セッションなら別キーにします。</xltc:text>
+  <xltc:threadedComment ref="A3" dT="2026-07-17T01:51:00.933" personId="{95263565-8673-4D96-B8C3-79834C7CE147}" id="{4032D6A1-2FD9-29E0-FF43-3A44EC59411B}">
+    <xltc:text>JSONのid。タイムテーブルの会場IDと完全一致させます。表示名と同じでも構いません。</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="F3" dT="2026-07-17T01:39:44.699" personId="{A60E5E94-04BA-4CF6-837C-AB1B77B12843}" id="{468BB692-D34D-1455-D890-17146C1FF036}">
-    <xltc:text>セッション全体のnote。項目ごとの説明はプログラム項目側へ入力します。</xltc:text>
+  <xltc:threadedComment ref="B3" dT="2026-07-17T01:51:00.933" personId="{95263565-8673-4D96-B8C3-79834C7CE147}" id="{EC798C26-A0B2-4406-AE60-A1507E8830B2}">
+    <xltc:text>JSONのname。例: 会場ID『講堂』、表示名『3階・講堂』。</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
 </file>
 
 <file path=xl/threadedcomments/threadedcomment4.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="A3" dT="2026-07-17T01:39:44.729" personId="{A60E5E94-04BA-4CF6-837C-AB1B77B12843}" id="{5F8066C5-957B-0CA7-B46B-5499ABC81DDC}">
+  <xltc:threadedComment ref="A3" dT="2026-07-17T01:51:00.963" personId="{95263565-8673-4D96-B8C3-79834C7CE147}" id="{8294C550-DF34-22FA-7AF3-1BA6051DD935}">
+    <xltc:text>同じセッションにまとめる行は同じキー（例: day1-07）。時刻や区分が同じでも別セッションなら別キーにします。</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="F3" dT="2026-07-17T01:51:00.963" personId="{95263565-8673-4D96-B8C3-79834C7CE147}" id="{B2E96024-59FC-4AE2-2922-B81DDE300CCC}">
+    <xltc:text>セッション全体のnote。項目ごとの説明はプログラム項目側へ入力します。</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="G3" dT="2026-07-17T01:51:00.964" personId="{95263565-8673-4D96-B8C3-79834C7CE147}" id="{8F2C0F5C-C3F5-B497-05D4-CB05FF018764}">
+    <xltc:text>afterNote。セッションのカード直後に表示する補足です（例: 終了後に懇親会を予定）。</xltc:text>
+  </xltc:threadedComment>
+</xltc:ThreadedComments>
+</file>
+
+<file path=xl/threadedcomments/threadedcomment5.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:threadedComment ref="A3" dT="2026-07-17T01:51:00.993" personId="{95263565-8673-4D96-B8C3-79834C7CE147}" id="{30A4B7D6-7F71-8869-053C-3625657D792A}">
     <xltc:text>セッションシートのキーと完全一致。受付・休憩などitemsが空のセッションは、このシートに行を作りません。</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B3" dT="2026-07-17T01:39:44.729" personId="{A60E5E94-04BA-4CF6-837C-AB1B77B12843}" id="{BD0FA2B3-28BC-B2E2-FFD2-8BE5600EA6DA}">
+  <xltc:threadedComment ref="B3" dT="2026-07-17T01:51:00.993" personId="{95263565-8673-4D96-B8C3-79834C7CE147}" id="{F225F0DF-A967-EE81-1A2F-216A4A045EE1}">
     <xltc:text>同一セッション内の表示順。1, 2, 3…を入力します。</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="F3" dT="2026-07-17T01:39:44.729" personId="{A60E5E94-04BA-4CF6-837C-AB1B77B12843}" id="{900A0A90-6C84-581E-DA86-45B310B77807}">
+  <xltc:threadedComment ref="F3" dT="2026-07-17T01:51:00.994" personId="{95263565-8673-4D96-B8C3-79834C7CE147}" id="{B218E4C8-2BF2-E501-1BD0-F950C4CCF1F2}">
     <xltc:text>items[].subtle。trueのとき細字・小サイズ。通常はfalseまたは空欄。</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -629,7 +671,7 @@
         <x:v>申込ページURL、公開チラシ、公開プログラムを渡す。資料にない内容は推測させない。</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
-        <x:v>参照元シートに資料名・URLを記録</x:v>
+        <x:v>参照元シートに資料名・URL・優先度を記録</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1216,9 +1258,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -1228,18 +1271,22 @@
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
       <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="9" t="str">
+        <x:v>優先度</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="str">
         <x:v>種別</x:v>
       </x:c>
-      <x:c r="B3" s="9" t="str">
+      <x:c r="C3" s="9" t="str">
         <x:v>資料名</x:v>
       </x:c>
-      <x:c r="C3" s="9" t="str">
+      <x:c r="D3" s="9" t="str">
         <x:v>URLまたはファイル名</x:v>
       </x:c>
-      <x:c r="D3" s="9" t="str">
+      <x:c r="E3" s="9" t="str">
         <x:v>参照範囲・備考</x:v>
       </x:c>
     </x:row>
@@ -1248,83 +1295,99 @@
       <x:c r="B4" s="16"/>
       <x:c r="C4" s="16"/>
       <x:c r="D4" s="16"/>
+      <x:c r="E4" s="16"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="17"/>
       <x:c r="B5" s="17"/>
       <x:c r="C5" s="17"/>
       <x:c r="D5" s="17"/>
+      <x:c r="E5" s="17"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="17"/>
       <x:c r="B6" s="17"/>
       <x:c r="C6" s="17"/>
       <x:c r="D6" s="17"/>
+      <x:c r="E6" s="17"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="17"/>
       <x:c r="B7" s="17"/>
       <x:c r="C7" s="17"/>
       <x:c r="D7" s="17"/>
+      <x:c r="E7" s="17"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="17"/>
       <x:c r="B8" s="17"/>
       <x:c r="C8" s="17"/>
       <x:c r="D8" s="17"/>
+      <x:c r="E8" s="17"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17"/>
       <x:c r="B9" s="17"/>
       <x:c r="C9" s="17"/>
       <x:c r="D9" s="17"/>
+      <x:c r="E9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17"/>
       <x:c r="B10" s="17"/>
       <x:c r="C10" s="17"/>
       <x:c r="D10" s="17"/>
+      <x:c r="E10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17"/>
       <x:c r="B11" s="17"/>
       <x:c r="C11" s="17"/>
       <x:c r="D11" s="17"/>
+      <x:c r="E11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17"/>
       <x:c r="B12" s="17"/>
       <x:c r="C12" s="17"/>
       <x:c r="D12" s="17"/>
+      <x:c r="E12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17"/>
       <x:c r="B13" s="17"/>
       <x:c r="C13" s="17"/>
       <x:c r="D13" s="17"/>
+      <x:c r="E13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17"/>
       <x:c r="B14" s="17"/>
       <x:c r="C14" s="17"/>
       <x:c r="D14" s="17"/>
+      <x:c r="E14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="18"/>
       <x:c r="B15" s="18"/>
       <x:c r="C15" s="18"/>
       <x:c r="D15" s="18"/>
+      <x:c r="E15" s="18"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="A4:A15">
+      <x:formula1>"1（最優先）,2,3"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="B4:B15">
       <x:formula1>"申込ページ,チラシ,プログラム,公式サイト,その他"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R829bcbf8cfc54d6d"/>
 </x:worksheet>
 </file>
 
@@ -1777,7 +1840,7 @@
     <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc79e2ebdfda4a31"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R292bc9b53e1a4fe4"/>
 </x:worksheet>
 </file>
 
@@ -1918,7 +1981,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdf56ad360e746fb"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7958dc58b35a48bc"/>
 </x:worksheet>
 </file>
 
@@ -1931,7 +1994,8 @@
     <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="52" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -1943,6 +2007,7 @@
       <x:c r="D1" s="3"/>
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="9" t="str">
@@ -1962,6 +2027,9 @@
       </x:c>
       <x:c r="F3" s="9" t="str">
         <x:v>セッション補足</x:v>
+      </x:c>
+      <x:c r="G3" s="9" t="str">
+        <x:v>セッション後補足</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1971,6 +2039,7 @@
       <x:c r="D4" s="24"/>
       <x:c r="E4" s="24"/>
       <x:c r="F4" s="24"/>
+      <x:c r="G4" s="24"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25"/>
@@ -1979,6 +2048,7 @@
       <x:c r="D5" s="25"/>
       <x:c r="E5" s="25"/>
       <x:c r="F5" s="25"/>
+      <x:c r="G5" s="25"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="25"/>
@@ -1987,6 +2057,7 @@
       <x:c r="D6" s="25"/>
       <x:c r="E6" s="25"/>
       <x:c r="F6" s="25"/>
+      <x:c r="G6" s="25"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="25"/>
@@ -1995,6 +2066,7 @@
       <x:c r="D7" s="25"/>
       <x:c r="E7" s="25"/>
       <x:c r="F7" s="25"/>
+      <x:c r="G7" s="25"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="25"/>
@@ -2003,6 +2075,7 @@
       <x:c r="D8" s="25"/>
       <x:c r="E8" s="25"/>
       <x:c r="F8" s="25"/>
+      <x:c r="G8" s="25"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="25"/>
@@ -2011,6 +2084,7 @@
       <x:c r="D9" s="25"/>
       <x:c r="E9" s="25"/>
       <x:c r="F9" s="25"/>
+      <x:c r="G9" s="25"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="25"/>
@@ -2019,6 +2093,7 @@
       <x:c r="D10" s="25"/>
       <x:c r="E10" s="25"/>
       <x:c r="F10" s="25"/>
+      <x:c r="G10" s="25"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="25"/>
@@ -2027,6 +2102,7 @@
       <x:c r="D11" s="25"/>
       <x:c r="E11" s="25"/>
       <x:c r="F11" s="25"/>
+      <x:c r="G11" s="25"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="25"/>
@@ -2035,6 +2111,7 @@
       <x:c r="D12" s="25"/>
       <x:c r="E12" s="25"/>
       <x:c r="F12" s="25"/>
+      <x:c r="G12" s="25"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="25"/>
@@ -2043,6 +2120,7 @@
       <x:c r="D13" s="25"/>
       <x:c r="E13" s="25"/>
       <x:c r="F13" s="25"/>
+      <x:c r="G13" s="25"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="25"/>
@@ -2051,6 +2129,7 @@
       <x:c r="D14" s="25"/>
       <x:c r="E14" s="25"/>
       <x:c r="F14" s="25"/>
+      <x:c r="G14" s="25"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="25"/>
@@ -2059,6 +2138,7 @@
       <x:c r="D15" s="25"/>
       <x:c r="E15" s="25"/>
       <x:c r="F15" s="25"/>
+      <x:c r="G15" s="25"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="25"/>
@@ -2067,6 +2147,7 @@
       <x:c r="D16" s="25"/>
       <x:c r="E16" s="25"/>
       <x:c r="F16" s="25"/>
+      <x:c r="G16" s="25"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="25"/>
@@ -2075,6 +2156,7 @@
       <x:c r="D17" s="25"/>
       <x:c r="E17" s="25"/>
       <x:c r="F17" s="25"/>
+      <x:c r="G17" s="25"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="25"/>
@@ -2083,6 +2165,7 @@
       <x:c r="D18" s="25"/>
       <x:c r="E18" s="25"/>
       <x:c r="F18" s="25"/>
+      <x:c r="G18" s="25"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="25"/>
@@ -2091,6 +2174,7 @@
       <x:c r="D19" s="25"/>
       <x:c r="E19" s="25"/>
       <x:c r="F19" s="25"/>
+      <x:c r="G19" s="25"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="25"/>
@@ -2099,6 +2183,7 @@
       <x:c r="D20" s="25"/>
       <x:c r="E20" s="25"/>
       <x:c r="F20" s="25"/>
+      <x:c r="G20" s="25"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="25"/>
@@ -2107,6 +2192,7 @@
       <x:c r="D21" s="25"/>
       <x:c r="E21" s="25"/>
       <x:c r="F21" s="25"/>
+      <x:c r="G21" s="25"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="25"/>
@@ -2115,6 +2201,7 @@
       <x:c r="D22" s="25"/>
       <x:c r="E22" s="25"/>
       <x:c r="F22" s="25"/>
+      <x:c r="G22" s="25"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="25"/>
@@ -2123,6 +2210,7 @@
       <x:c r="D23" s="25"/>
       <x:c r="E23" s="25"/>
       <x:c r="F23" s="25"/>
+      <x:c r="G23" s="25"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="25"/>
@@ -2131,6 +2219,7 @@
       <x:c r="D24" s="25"/>
       <x:c r="E24" s="25"/>
       <x:c r="F24" s="25"/>
+      <x:c r="G24" s="25"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="25"/>
@@ -2139,6 +2228,7 @@
       <x:c r="D25" s="25"/>
       <x:c r="E25" s="25"/>
       <x:c r="F25" s="25"/>
+      <x:c r="G25" s="25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="25"/>
@@ -2147,6 +2237,7 @@
       <x:c r="D26" s="25"/>
       <x:c r="E26" s="25"/>
       <x:c r="F26" s="25"/>
+      <x:c r="G26" s="25"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="25"/>
@@ -2155,6 +2246,7 @@
       <x:c r="D27" s="25"/>
       <x:c r="E27" s="25"/>
       <x:c r="F27" s="25"/>
+      <x:c r="G27" s="25"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="25"/>
@@ -2163,6 +2255,7 @@
       <x:c r="D28" s="25"/>
       <x:c r="E28" s="25"/>
       <x:c r="F28" s="25"/>
+      <x:c r="G28" s="25"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="25"/>
@@ -2171,6 +2264,7 @@
       <x:c r="D29" s="25"/>
       <x:c r="E29" s="25"/>
       <x:c r="F29" s="25"/>
+      <x:c r="G29" s="25"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="25"/>
@@ -2179,6 +2273,7 @@
       <x:c r="D30" s="25"/>
       <x:c r="E30" s="25"/>
       <x:c r="F30" s="25"/>
+      <x:c r="G30" s="25"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="25"/>
@@ -2187,6 +2282,7 @@
       <x:c r="D31" s="25"/>
       <x:c r="E31" s="25"/>
       <x:c r="F31" s="25"/>
+      <x:c r="G31" s="25"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="25"/>
@@ -2195,6 +2291,7 @@
       <x:c r="D32" s="25"/>
       <x:c r="E32" s="25"/>
       <x:c r="F32" s="25"/>
+      <x:c r="G32" s="25"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="25"/>
@@ -2203,6 +2300,7 @@
       <x:c r="D33" s="25"/>
       <x:c r="E33" s="25"/>
       <x:c r="F33" s="25"/>
+      <x:c r="G33" s="25"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="25"/>
@@ -2211,6 +2309,7 @@
       <x:c r="D34" s="25"/>
       <x:c r="E34" s="25"/>
       <x:c r="F34" s="25"/>
+      <x:c r="G34" s="25"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="25"/>
@@ -2219,6 +2318,7 @@
       <x:c r="D35" s="25"/>
       <x:c r="E35" s="25"/>
       <x:c r="F35" s="25"/>
+      <x:c r="G35" s="25"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="25"/>
@@ -2227,6 +2327,7 @@
       <x:c r="D36" s="25"/>
       <x:c r="E36" s="25"/>
       <x:c r="F36" s="25"/>
+      <x:c r="G36" s="25"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="25"/>
@@ -2235,6 +2336,7 @@
       <x:c r="D37" s="25"/>
       <x:c r="E37" s="25"/>
       <x:c r="F37" s="25"/>
+      <x:c r="G37" s="25"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="25"/>
@@ -2243,6 +2345,7 @@
       <x:c r="D38" s="25"/>
       <x:c r="E38" s="25"/>
       <x:c r="F38" s="25"/>
+      <x:c r="G38" s="25"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="25"/>
@@ -2251,6 +2354,7 @@
       <x:c r="D39" s="25"/>
       <x:c r="E39" s="25"/>
       <x:c r="F39" s="25"/>
+      <x:c r="G39" s="25"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="25"/>
@@ -2259,6 +2363,7 @@
       <x:c r="D40" s="25"/>
       <x:c r="E40" s="25"/>
       <x:c r="F40" s="25"/>
+      <x:c r="G40" s="25"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="25"/>
@@ -2267,6 +2372,7 @@
       <x:c r="D41" s="25"/>
       <x:c r="E41" s="25"/>
       <x:c r="F41" s="25"/>
+      <x:c r="G41" s="25"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="25"/>
@@ -2275,6 +2381,7 @@
       <x:c r="D42" s="25"/>
       <x:c r="E42" s="25"/>
       <x:c r="F42" s="25"/>
+      <x:c r="G42" s="25"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="25"/>
@@ -2283,6 +2390,7 @@
       <x:c r="D43" s="25"/>
       <x:c r="E43" s="25"/>
       <x:c r="F43" s="25"/>
+      <x:c r="G43" s="25"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="25"/>
@@ -2291,6 +2399,7 @@
       <x:c r="D44" s="25"/>
       <x:c r="E44" s="25"/>
       <x:c r="F44" s="25"/>
+      <x:c r="G44" s="25"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="25"/>
@@ -2299,6 +2408,7 @@
       <x:c r="D45" s="25"/>
       <x:c r="E45" s="25"/>
       <x:c r="F45" s="25"/>
+      <x:c r="G45" s="25"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="25"/>
@@ -2307,6 +2417,7 @@
       <x:c r="D46" s="25"/>
       <x:c r="E46" s="25"/>
       <x:c r="F46" s="25"/>
+      <x:c r="G46" s="25"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="25"/>
@@ -2315,6 +2426,7 @@
       <x:c r="D47" s="25"/>
       <x:c r="E47" s="25"/>
       <x:c r="F47" s="25"/>
+      <x:c r="G47" s="25"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="25"/>
@@ -2323,6 +2435,7 @@
       <x:c r="D48" s="25"/>
       <x:c r="E48" s="25"/>
       <x:c r="F48" s="25"/>
+      <x:c r="G48" s="25"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="25"/>
@@ -2331,6 +2444,7 @@
       <x:c r="D49" s="25"/>
       <x:c r="E49" s="25"/>
       <x:c r="F49" s="25"/>
+      <x:c r="G49" s="25"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="25"/>
@@ -2339,6 +2453,7 @@
       <x:c r="D50" s="25"/>
       <x:c r="E50" s="25"/>
       <x:c r="F50" s="25"/>
+      <x:c r="G50" s="25"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="25"/>
@@ -2347,6 +2462,7 @@
       <x:c r="D51" s="25"/>
       <x:c r="E51" s="25"/>
       <x:c r="F51" s="25"/>
+      <x:c r="G51" s="25"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="25"/>
@@ -2355,6 +2471,7 @@
       <x:c r="D52" s="25"/>
       <x:c r="E52" s="25"/>
       <x:c r="F52" s="25"/>
+      <x:c r="G52" s="25"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="26"/>
@@ -2363,13 +2480,14 @@
       <x:c r="D53" s="26"/>
       <x:c r="E53" s="26"/>
       <x:c r="F53" s="26"/>
+      <x:c r="G53" s="26"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:G1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6ef059d6785482c"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad604505ba05454d"/>
 </x:worksheet>
 </file>
 
@@ -3225,7 +3343,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re59a54babc4c4939"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re602acf7e0cc4bed"/>
 </x:worksheet>
 </file>
 

--- a/template/イベント情報入力シート.xlsx
+++ b/template/イベント情報入力シート.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="1" r:id="R92c5771f67454bc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="R9faefbeae547480d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本情報" sheetId="3" r:id="R10eff51424ad4728"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="開催日" sheetId="4" r:id="R85b60e9f19194fb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会場" sheetId="5" r:id="R94cee4d2af06427e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セッション" sheetId="6" r:id="Rb8cbbde3840d489f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プログラム項目" sheetId="7" r:id="R37bcc90d2fe945ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料リンク" sheetId="8" r:id="R79e14f46d83e48d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連書籍" sheetId="9" r:id="R106b5fc90efa4a15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要・お知らせ" sheetId="10" r:id="Rd9a4dc4138964789"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認" sheetId="11" r:id="R9550b5f8208c481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力ガイド" sheetId="1" r:id="R6398991d58b44972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参照元" sheetId="2" r:id="R50ca55095c3445d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本情報" sheetId="3" r:id="Ra9ba6abd9d2b477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="開催日" sheetId="4" r:id="R21c3bd075d2f44ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会場" sheetId="5" r:id="Rc18931eda8e34f41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セッション" sheetId="6" r:id="R0a9f8f448a1c4345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プログラム項目" sheetId="7" r:id="Rea1fafdf4a5d416c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料リンク" sheetId="8" r:id="R9e13679e899a4592"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連書籍" sheetId="9" r:id="R8760ee4696da452f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要・お知らせ" sheetId="10" r:id="Ra559bcbfc4e64905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認" sheetId="11" r:id="R243499988d3c496f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1387,7 +1387,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R829bcbf8cfc54d6d"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02d2bb91928d4bbd"/>
 </x:worksheet>
 </file>
 
@@ -1473,231 +1473,243 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="17" t="str">
-        <x:v>アイコン3文字</x:v>
-      </x:c>
-      <x:c r="B8" s="25"/>
+        <x:v>ブックマーク名</x:v>
+      </x:c>
+      <x:c r="B8" s="25" t="str"/>
       <x:c r="C8" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
-        <x:v>iconLabel。未入力ならlogoMain先頭3文字</x:v>
+        <x:v>bookmarkName。未入力ならアプリ名（短め）</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="str">
-        <x:v>ロゴ補足</x:v>
+        <x:v>アイコン3文字</x:v>
       </x:c>
       <x:c r="B9" s="25"/>
       <x:c r="C9" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D9" s="17" t="str">
-        <x:v>logoSub</x:v>
+        <x:v>iconLabel。未入力ならlogoMain先頭3文字</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
-        <x:v>テーマ</x:v>
+        <x:v>ロゴ補足</x:v>
       </x:c>
       <x:c r="B10" s="25"/>
       <x:c r="C10" s="17" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="D10" s="17" t="str">
-        <x:v>theme。サブテーマを含む全文</x:v>
+        <x:v>logoSub</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
-        <x:v>会場名</x:v>
+        <x:v>テーマ</x:v>
       </x:c>
       <x:c r="B11" s="25"/>
       <x:c r="C11" s="17" t="str">
         <x:v>必須</x:v>
       </x:c>
       <x:c r="D11" s="17" t="str">
-        <x:v>venueName。オンラインの場合も資料表記に従う</x:v>
+        <x:v>theme。サブテーマを含む全文</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
-        <x:v>開催日（表示用）</x:v>
+        <x:v>会場名</x:v>
       </x:c>
       <x:c r="B12" s="25"/>
       <x:c r="C12" s="17" t="str">
         <x:v>必須</x:v>
       </x:c>
       <x:c r="D12" s="17" t="str">
-        <x:v>dateRange。画面に出す表記</x:v>
+        <x:v>venueName。オンラインの場合も資料表記に従う</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
-        <x:v>主催</x:v>
+        <x:v>開催日（表示用）</x:v>
       </x:c>
       <x:c r="B13" s="25"/>
       <x:c r="C13" s="17" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="D13" s="17" t="str">
-        <x:v>organizer。複数はセル内改行で1団体ずつ</x:v>
+        <x:v>dateRange。画面に出す表記</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
-        <x:v>共催</x:v>
+        <x:v>主催</x:v>
       </x:c>
       <x:c r="B14" s="25"/>
       <x:c r="C14" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
-        <x:v>coOrganizer。複数はセル内改行</x:v>
+        <x:v>organizer。複数はセル内改行で1団体ずつ</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
-        <x:v>協力</x:v>
+        <x:v>共催</x:v>
       </x:c>
       <x:c r="B15" s="25"/>
       <x:c r="C15" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D15" s="17" t="str">
-        <x:v>cooperation。複数はセル内改行</x:v>
+        <x:v>coOrganizer。複数はセル内改行</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
-        <x:v>後援</x:v>
+        <x:v>協力</x:v>
       </x:c>
       <x:c r="B16" s="25"/>
       <x:c r="C16" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D16" s="17" t="str">
-        <x:v>support。複数はセル内改行</x:v>
+        <x:v>cooperation。複数はセル内改行</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
-        <x:v>ブランド色</x:v>
+        <x:v>後援</x:v>
       </x:c>
       <x:c r="B17" s="25"/>
       <x:c r="C17" s="17" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>brandColor。# + 6桁16進</x:v>
+        <x:v>support。複数はセル内改行</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="17" t="str">
-        <x:v>補助ブランド色</x:v>
+        <x:v>ブランド色</x:v>
       </x:c>
       <x:c r="B18" s="25"/>
       <x:c r="C18" s="17" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="D18" s="17" t="str">
-        <x:v>brandColor2。# + 6桁16進</x:v>
+        <x:v>brandColor。# + 6桁16進</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="17" t="str">
-        <x:v>イベントID</x:v>
+        <x:v>補助ブランド色</x:v>
       </x:c>
       <x:c r="B19" s="25"/>
       <x:c r="C19" s="17" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="D19" s="17" t="str">
-        <x:v>半角英数・ハイフン・アンダースコアのみ</x:v>
+        <x:v>brandColor2。# + 6桁16進</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="17" t="str">
-        <x:v>並び順日付</x:v>
+        <x:v>イベントID</x:v>
       </x:c>
       <x:c r="B20" s="25"/>
       <x:c r="C20" s="17" t="str">
         <x:v>必須</x:v>
       </x:c>
       <x:c r="D20" s="17" t="str">
-        <x:v>sortDate。YYYY-MM-DD</x:v>
+        <x:v>半角英数・ハイフン・アンダースコアのみ</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="17" t="str">
-        <x:v>LINE追加ポップアップ</x:v>
-      </x:c>
-      <x:c r="B21" s="25" t="str">
-        <x:v>false</x:v>
-      </x:c>
+        <x:v>並び順日付</x:v>
+      </x:c>
+      <x:c r="B21" s="25"/>
       <x:c r="C21" s="17" t="str">
         <x:v>必須</x:v>
       </x:c>
       <x:c r="D21" s="17" t="str">
-        <x:v>linePromo。true / false</x:v>
+        <x:v>sortDate。YYYY-MM-DD</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="17" t="str">
-        <x:v>会場マップ補足</x:v>
-      </x:c>
-      <x:c r="B22" s="25"/>
+        <x:v>LINE追加ポップアップ</x:v>
+      </x:c>
+      <x:c r="B22" s="25" t="str">
+        <x:v>false</x:v>
+      </x:c>
       <x:c r="C22" s="17" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="D22" s="17" t="str">
-        <x:v>venue.mapNote</x:v>
+        <x:v>linePromo。true / false</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="17" t="str">
-        <x:v>会場マップ画像</x:v>
+        <x:v>会場マップ補足</x:v>
       </x:c>
       <x:c r="B23" s="25"/>
       <x:c r="C23" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D23" s="17" t="str">
-        <x:v>venue.mapImage。相対パスまたは公開URL</x:v>
+        <x:v>venue.mapNote</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="17" t="str">
-        <x:v>書籍特設販売URL</x:v>
+        <x:v>会場マップ画像</x:v>
       </x:c>
       <x:c r="B24" s="25"/>
       <x:c r="C24" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D24" s="17" t="str">
-        <x:v>bookSale.url</x:v>
+        <x:v>venue.mapImage。相対パスまたは公開URL</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="17" t="str">
-        <x:v>書籍特設販売ラベル</x:v>
+        <x:v>書籍特設販売URL</x:v>
       </x:c>
       <x:c r="B25" s="25"/>
       <x:c r="C25" s="17" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D25" s="17" t="str">
-        <x:v>bookSale.label</x:v>
+        <x:v>bookSale.url</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="18" t="str">
-        <x:v>書籍特設販売補足</x:v>
+        <x:v>書籍特設販売ラベル</x:v>
       </x:c>
       <x:c r="B26" s="26"/>
       <x:c r="C26" s="18" t="str">
         <x:v>任意</x:v>
       </x:c>
       <x:c r="D26" s="18" t="str">
+        <x:v>bookSale.label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>書籍特設販売補足</x:v>
+      </x:c>
+      <x:c r="B27"/>
+      <x:c r="C27" t="str">
+        <x:v>任意</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
         <x:v>bookSale.note</x:v>
       </x:c>
     </x:row>
@@ -1840,7 +1852,7 @@
     <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R292bc9b53e1a4fe4"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c0ab36b7baf493c"/>
 </x:worksheet>
 </file>
 
@@ -1981,7 +1993,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7958dc58b35a48bc"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8338f615666a41bc"/>
 </x:worksheet>
 </file>
 
@@ -2487,7 +2499,7 @@
     <x:mergeCell ref="A1:G1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad604505ba05454d"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R309e6b9e312148d1"/>
 </x:worksheet>
 </file>
 
@@ -3343,7 +3355,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re602acf7e0cc4bed"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0ec9702319a4ed5"/>
 </x:worksheet>
 </file>
 
